--- a/Product_Database.xlsx
+++ b/Product_Database.xlsx
@@ -1619,7 +1619,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Chair 06 A1 [1S-LE-N]</t>
+          <t>Chair 06 A1 [1S-FB-N]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>255</v>
+        <v>205</v>
       </c>
       <c r="E52" t="n">
         <v>75</v>
@@ -2764,7 +2764,7 @@
         <v>84</v>
       </c>
       <c r="G52" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K52" s="6" t="inlineStr">
         <is>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E54" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F54" t="n">
         <v>110</v>
@@ -2853,10 +2853,33 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Living</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>product is in theme 1 &amp; umang</t>
-        </is>
+          <t>Storage 29 C2 [STD-XX-N]</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Storage 29 C2</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>149</v>
+      </c>
+      <c r="E55" t="n">
+        <v>42</v>
+      </c>
+      <c r="F55" t="n">
+        <v>181</v>
+      </c>
+      <c r="I55">
+        <f>D55 &amp; "cm x " &amp; E55 &amp; "cm x " &amp; F55 &amp; "cm (H) x SH-" &amp; G55 &amp; "cm"</f>
+        <v/>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
@@ -2865,8 +2888,11 @@
       </c>
       <c r="L55" s="6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R55" t="n">
+        <v>149000</v>
       </c>
     </row>
     <row r="56">

--- a/Product_Database.xlsx
+++ b/Product_Database.xlsx
@@ -2052,23 +2052,40 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Outdoor</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Bench 14 A1 [2S-FB-N]</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Bench 14 A1</t>
+        </is>
+      </c>
       <c r="D35" t="n">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="E35" t="n">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="F35" t="n">
-        <v>56</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>94cm x 30cm x 56cm (H) x SH-cm</t>
-        </is>
+        <v>88</v>
+      </c>
+      <c r="G35" t="n">
+        <v>45</v>
+      </c>
+      <c r="I35">
+        <f>D35 &amp; "cm x " &amp; E35 &amp; "cm x " &amp; F35 &amp; "cm (H) x SH-" &amp; G35 &amp; "cm"</f>
+        <v/>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
